--- a/excels/demo - BIG.xlsx
+++ b/excels/demo - BIG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radin\Documents\Adi Heavy\Siraal\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F33167-8019-45C8-B575-D107810A9A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4DBACC-2FE6-4984-82C7-6CD685CF06EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1863,7 +1863,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>30</v>
